--- a/resources/digital-products/files/dp-basics-pricing-sum.xlsx
+++ b/resources/digital-products/files/dp-basics-pricing-sum.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="£#,##0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -529,7 +529,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -575,7 +575,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Price (£)</t>
+          <t>Price ($)</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -598,14 +598,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>your platform's all-in cut — Whop ~6, Etsy ~10, Gumroad ~13</t>
+          <t>all-in cut at about $24 — Whop ~4, Etsy ~11, Gumroad ~16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Income you want per month (£)</t>
+          <t>Income you want per month ($)</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
@@ -637,7 +637,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Kept per sale (£)</t>
+          <t>Kept per sale ($)</t>
         </is>
       </c>
       <c r="B12" s="10">
@@ -680,7 +680,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Worked example from the book: £24 at 6.5% keeps £22.44; 23 sales clear £500; that needs 1,150 visitors.</t>
+          <t>Worked example from the book: $24 at 6.5% keeps $22.44; 23 sales clear $500; that needs 1,150 visitors.</t>
         </is>
       </c>
     </row>
@@ -708,5 +708,6 @@
     <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-basics-pricing-sum.xlsx
+++ b/resources/digital-products/files/dp-basics-pricing-sum.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -565,6 +565,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -627,6 +628,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -677,6 +679,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -684,6 +687,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="13" t="n"/>
@@ -696,12 +700,17 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
